--- a/data/contact-messages.xlsx
+++ b/data/contact-messages.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F18"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="25.83203125" customWidth="1"/>
@@ -707,9 +707,69 @@
         <v>asdfghjkl;</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>14/10/2025, 05:42 pm</v>
+      </c>
+      <c r="B16" t="str">
+        <v>pqrst</v>
+      </c>
+      <c r="C16" t="str">
+        <v>09424309363</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Bridal &amp; Party Styling</v>
+      </c>
+      <c r="E16" t="str">
+        <v>Kadubeesanhalli, Sarjapur Road, Near Krishna Tech Park</v>
+      </c>
+      <c r="F16" t="str">
+        <v>testing for the services</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>15/10/2025, 10:26 am</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Email Test User</v>
+      </c>
+      <c r="C17" t="str">
+        <v>9876543210</v>
+      </c>
+      <c r="D17" t="str">
+        <v>Hair Services</v>
+      </c>
+      <c r="E17" t="str">
+        <v>Test Address</v>
+      </c>
+      <c r="F17" t="str">
+        <v>Testing email configuration</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>15/10/2025, 10:26 am</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Email Test User</v>
+      </c>
+      <c r="C18" t="str">
+        <v>9876543210</v>
+      </c>
+      <c r="D18" t="str">
+        <v>Hair Services</v>
+      </c>
+      <c r="E18" t="str">
+        <v>Test Address</v>
+      </c>
+      <c r="F18" t="str">
+        <v>Testing email configuration</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F15"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F18"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/contact-messages.xlsx
+++ b/data/contact-messages.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F24"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="25.83203125" customWidth="1"/>
@@ -767,9 +767,129 @@
         <v>Testing email configuration</v>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>21/10/2025, 06:28 pm</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Sailakhsmi</v>
+      </c>
+      <c r="C19" t="str">
+        <v>09424309363</v>
+      </c>
+      <c r="D19" t="str">
+        <v>Women's Hair Services</v>
+      </c>
+      <c r="E19" t="str">
+        <v>Kadubeesanhalli, Sarjapur Road, Near Krishna Tech Park</v>
+      </c>
+      <c r="F19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>22/10/2025, 09:52 am</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Test</v>
+      </c>
+      <c r="C20" t="str">
+        <v>1234567890</v>
+      </c>
+      <c r="D20" t="str">
+        <v>Haircut</v>
+      </c>
+      <c r="E20" t="str">
+        <v>Test Address</v>
+      </c>
+      <c r="F20" t="str">
+        <v>Test message</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>22/10/2025, 09:53 am</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Test</v>
+      </c>
+      <c r="C21" t="str">
+        <v>1234567890</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Haircut</v>
+      </c>
+      <c r="E21" t="str">
+        <v>Test Address</v>
+      </c>
+      <c r="F21" t="str">
+        <v>Test message</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>22/10/2025, 04:36 pm</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Test User</v>
+      </c>
+      <c r="C22" t="str">
+        <v>+1234567890</v>
+      </c>
+      <c r="D22" t="str">
+        <v>Hair Cut</v>
+      </c>
+      <c r="E22" t="str">
+        <v>123 Test Street</v>
+      </c>
+      <c r="F22" t="str">
+        <v>This is a test message</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>22/10/2025, 05:10 pm</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Test Booking User</v>
+      </c>
+      <c r="C23" t="str">
+        <v>+9876543210</v>
+      </c>
+      <c r="D23" t="str">
+        <v>Hair Cut &amp; Styling</v>
+      </c>
+      <c r="E23" t="str">
+        <v>456 Test Avenue</v>
+      </c>
+      <c r="F23" t="str">
+        <v>I want to book a hair cut service</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>22/10/2025, 05:34 pm</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Test User MongoDB</v>
+      </c>
+      <c r="C24" t="str">
+        <v>+1234567890</v>
+      </c>
+      <c r="D24" t="str">
+        <v>Hair Cut &amp; Styling</v>
+      </c>
+      <c r="E24" t="str">
+        <v>123 Test Street</v>
+      </c>
+      <c r="F24" t="str">
+        <v>Testing MongoDB integration</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F18"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F24"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/contact-messages.xlsx
+++ b/data/contact-messages.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F2"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="25.83203125" customWidth="1"/>
@@ -427,349 +427,31 @@
         <v>Message</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" xml:space="preserve">
       <c r="A2" t="str">
-        <v>10/10/2025, 01:37 pm</v>
+        <v>06/11/2025, 11:50 pm</v>
       </c>
       <c r="B2" t="str">
-        <v>Test User</v>
+        <v>vamshi v</v>
       </c>
       <c r="C2" t="str">
-        <v>1234567890</v>
+        <v>07032469246</v>
       </c>
       <c r="D2" t="str">
-        <v>Women's Hair Services</v>
-      </c>
-      <c r="E2" t="str">
-        <v>123 Test St</v>
-      </c>
-      <c r="F2" t="str">
-        <v>Test message from API fix</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>10/10/2025, 02:36 pm</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Test Customer</v>
-      </c>
-      <c r="C3" t="str">
-        <v>1234567890</v>
-      </c>
-      <c r="D3" t="str">
-        <v>Women Hair Services</v>
-      </c>
-      <c r="E3" t="str">
-        <v>123 Test Street</v>
-      </c>
-      <c r="F3" t="str">
-        <v>I need a haircut. Please call me.</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>10/10/2025, 02:38 pm</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Sailakhsmi</v>
-      </c>
-      <c r="C4" t="str">
-        <v>09424309363</v>
-      </c>
-      <c r="D4" t="str">
-        <v>Hair Coloring</v>
-      </c>
-      <c r="E4" t="str">
-        <v>Kadubeesanhalli, Sarjapur Road, Near Krishna Tech Park</v>
-      </c>
-      <c r="F4" t="str">
-        <v>hiiiiiiiiiiiiiiiiiiiiiiiiiiiii</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>10/10/2025, 02:41 pm</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Final Test</v>
-      </c>
-      <c r="C5" t="str">
-        <v>9876543210</v>
-      </c>
-      <c r="D5" t="str">
-        <v>Women Hair Services</v>
-      </c>
-      <c r="E5" t="str">
-        <v>456 Beauty Street</v>
-      </c>
-      <c r="F5" t="str">
-        <v>Testing email after dotenv fix. Please call me!</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>10/10/2025, 02:43 pm</v>
-      </c>
-      <c r="B6" t="str">
-        <v>Sailakhsmi</v>
-      </c>
-      <c r="C6" t="str">
-        <v>09424309363</v>
-      </c>
-      <c r="D6" t="str">
         <v>Kids Hair Services</v>
       </c>
-      <c r="E6" t="str">
-        <v>Kadubeesanhalli, Sarjapur Road, Near Krishna Tech Park</v>
-      </c>
-      <c r="F6" t="str">
-        <v>hiiiiiiiiiiiiiiiiiiiiiiiiiiiiiiiiii</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>10/10/2025, 02:47 pm</v>
-      </c>
-      <c r="B7" t="str">
-        <v>testing user</v>
-      </c>
-      <c r="C7" t="str">
-        <v>1234567890</v>
-      </c>
-      <c r="D7" t="str">
-        <v>Kids Hair Services</v>
-      </c>
-      <c r="E7" t="str">
-        <v>Kadubeesanhalli, Sarjapur Road, Near Krishna Tech Park</v>
-      </c>
-      <c r="F7" t="str">
-        <v>testing the email serviice</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>10/10/2025, 04:17 pm</v>
-      </c>
-      <c r="B8" t="str">
-        <v>Beautiful Design Test</v>
-      </c>
-      <c r="C8" t="str">
-        <v>9876543210</v>
-      </c>
-      <c r="D8" t="str">
-        <v>Women Hair Services</v>
-      </c>
-      <c r="E8" t="str">
-        <v>123 Glamour Street, Bangalore</v>
-      </c>
-      <c r="F8" t="str">
-        <v>Hi! I love the new design! I want to book a hair styling appointment for next week. Please call me back at your earliest convenience. Thank you!</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>10/10/2025, 04:19 pm</v>
-      </c>
-      <c r="B9" t="str">
-        <v>Sailakhsmi</v>
-      </c>
-      <c r="C9" t="str">
-        <v>1234567890</v>
-      </c>
-      <c r="D9" t="str">
-        <v>Hair Spa &amp; Treatment</v>
-      </c>
-      <c r="E9" t="str">
-        <v>Kadubeesanhalli, Sarjapur Road, Near Krishna Tech Park</v>
-      </c>
-      <c r="F9" t="str">
-        <v>checking ui of the email template</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>10/10/2025, 04:24 pm</v>
-      </c>
-      <c r="B10" t="str">
-        <v>Elegant Design Test</v>
-      </c>
-      <c r="C10" t="str">
-        <v>9876543210</v>
-      </c>
-      <c r="D10" t="str">
-        <v>Bridal Hair Styling</v>
-      </c>
-      <c r="E10" t="str">
-        <v>456 Blossom Avenue, Bangalore</v>
-      </c>
-      <c r="F10" t="str">
-        <v>Hello! I am interested in your bridal hair styling service for my wedding next month. The new elegant design looks beautiful! Please call me to discuss the details and pricing. Thank you!</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>11/10/2025, 01:15 pm</v>
-      </c>
-      <c r="B11" t="str">
-        <v>tanu</v>
-      </c>
-      <c r="C11" t="str">
-        <v>09424309363</v>
-      </c>
-      <c r="D11" t="str">
-        <v>Bridal &amp; Party Styling</v>
-      </c>
-      <c r="E11" t="str">
-        <v>Kadubeesanhalli, Sarjapur Road, Near Krishna Tech Park</v>
-      </c>
-      <c r="F11" t="str">
-        <v>hi</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>11/10/2025, 03:08 pm</v>
-      </c>
-      <c r="B12" t="str">
-        <v>Sailakhsmi</v>
-      </c>
-      <c r="C12" t="str">
-        <v>1234567890</v>
-      </c>
-      <c r="D12" t="str">
-        <v>Bridal &amp; Party Styling</v>
-      </c>
-      <c r="E12" t="str">
-        <v>Kadubeesanhalli, Sarjapur Road, Near Krishna Tech Park</v>
-      </c>
-      <c r="F12" t="str">
-        <v>hi</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>11/10/2025, 03:11 pm</v>
-      </c>
-      <c r="B13" t="str">
-        <v>Sailakhsmi</v>
-      </c>
-      <c r="C13" t="str">
-        <v>1234567890</v>
-      </c>
-      <c r="D13" t="str">
-        <v>Kids Hair Services</v>
-      </c>
-      <c r="E13" t="str">
-        <v>Kadubeesanhalli, Sarjapur Road, Near Krishna Tech Park</v>
-      </c>
-      <c r="F13" t="str">
-        <v>tell us about your services</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>11/10/2025, 03:27 pm</v>
-      </c>
-      <c r="B14" t="str">
-        <v>Saiiiii</v>
-      </c>
-      <c r="C14" t="str">
-        <v>12</v>
-      </c>
-      <c r="D14" t="str">
-        <v>Hair Coloring</v>
-      </c>
-      <c r="E14" t="str">
-        <v>Kadubeesanhalli, Sarjapur Road, Near Krishna Tech Park</v>
-      </c>
-      <c r="F14" t="str">
-        <v>testing</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>11/10/2025, 03:37 pm</v>
-      </c>
-      <c r="B15" t="str">
-        <v>abc</v>
-      </c>
-      <c r="C15" t="str">
-        <v>66666666666</v>
-      </c>
-      <c r="D15" t="str">
-        <v>Bridal &amp; Party Styling</v>
-      </c>
-      <c r="E15" t="str">
-        <v>Kadubeesanhalli, Sarjapur Road, Near Krishna Tech Park</v>
-      </c>
-      <c r="F15" t="str">
-        <v>asdfghjkl;</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>14/10/2025, 05:42 pm</v>
-      </c>
-      <c r="B16" t="str">
-        <v>pqrst</v>
-      </c>
-      <c r="C16" t="str">
-        <v>09424309363</v>
-      </c>
-      <c r="D16" t="str">
-        <v>Bridal &amp; Party Styling</v>
-      </c>
-      <c r="E16" t="str">
-        <v>Kadubeesanhalli, Sarjapur Road, Near Krishna Tech Park</v>
-      </c>
-      <c r="F16" t="str">
-        <v>testing for the services</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>15/10/2025, 10:26 am</v>
-      </c>
-      <c r="B17" t="str">
-        <v>Email Test User</v>
-      </c>
-      <c r="C17" t="str">
-        <v>9876543210</v>
-      </c>
-      <c r="D17" t="str">
-        <v>Hair Services</v>
-      </c>
-      <c r="E17" t="str">
-        <v>Test Address</v>
-      </c>
-      <c r="F17" t="str">
-        <v>Testing email configuration</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>15/10/2025, 10:26 am</v>
-      </c>
-      <c r="B18" t="str">
-        <v>Email Test User</v>
-      </c>
-      <c r="C18" t="str">
-        <v>9876543210</v>
-      </c>
-      <c r="D18" t="str">
-        <v>Hair Services</v>
-      </c>
-      <c r="E18" t="str">
-        <v>Test Address</v>
-      </c>
-      <c r="F18" t="str">
-        <v>Testing email configuration</v>
+      <c r="E2" t="str" xml:space="preserve">
+        <v xml:space="preserve">Lovely professional University
+Lovely professional University</v>
+      </c>
+      <c r="F2" t="str" xml:space="preserve">
+        <v xml:space="preserve">doorstep service required
+</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F18"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F2"/>
   </ignoredErrors>
 </worksheet>
 </file>